--- a/GroupI_Project2_GanntChart.xlsx
+++ b/GroupI_Project2_GanntChart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofnebraska-my.sharepoint.com/personal/29808448_nebraska_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofnebraska-my.sharepoint.com/personal/07334281_nebraska_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F06AD47B-6155-4435-B73D-770C46C39553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6C60029-AD30-4C7B-A205-9E1A90A13E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -141,7 +141,7 @@
     <t>Written Technical Report</t>
   </si>
   <si>
-    <t>All</t>
+    <t>Brock,  Bryce</t>
   </si>
   <si>
     <t>* Introduction/Background</t>
@@ -214,7 +214,7 @@
     <numFmt numFmtId="166" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="d"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,7 +784,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -912,9 +912,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="3" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1077,15 +1074,18 @@
     <xf numFmtId="0" fontId="18" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1098,9 +1098,6 @@
     <xf numFmtId="0" fontId="18" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -1700,7 +1697,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BL34"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.75" style="13" customWidth="1"/>
     <col min="2" max="2" width="49.25" customWidth="1"/>
@@ -1713,72 +1710,72 @@
     <col min="9" max="65" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="90" customHeight="1">
+    <row r="1" spans="1:64" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A1" s="14"/>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
       <c r="P1" s="19"/>
-      <c r="Q1" s="105">
+      <c r="Q1" s="106">
         <f>46059</f>
         <v>46059</v>
       </c>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-    </row>
-    <row r="2" spans="1:64" ht="30" customHeight="1">
-      <c r="B2" s="98" t="s">
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+    </row>
+    <row r="2" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
       <c r="F2" s="18"/>
-      <c r="I2" s="106" t="s">
+      <c r="I2" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
       <c r="P2" s="19"/>
       <c r="Q2" s="104">
         <v>1</v>
       </c>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
-    </row>
-    <row r="3" spans="1:64" s="21" customFormat="1" ht="30" customHeight="1">
+      <c r="R2" s="105"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="105"/>
+      <c r="U2" s="105"/>
+      <c r="V2" s="105"/>
+      <c r="W2" s="105"/>
+      <c r="X2" s="105"/>
+      <c r="Y2" s="105"/>
+      <c r="Z2" s="105"/>
+    </row>
+    <row r="3" spans="1:64" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="20" t="s">
         <v>4</v>
@@ -1786,108 +1783,108 @@
       <c r="D3" s="22"/>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:64" s="21" customFormat="1" ht="30" customHeight="1">
+    <row r="4" spans="1:64" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
       <c r="B4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="25"/>
-      <c r="I4" s="102">
+      <c r="I4" s="101">
         <f>I5</f>
         <v>46055</v>
       </c>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100">
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>46062</v>
       </c>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="100"/>
-      <c r="W4" s="100">
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="99"/>
+      <c r="U4" s="99"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>46069</v>
       </c>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-      <c r="AC4" s="100"/>
-      <c r="AD4" s="100">
+      <c r="X4" s="99"/>
+      <c r="Y4" s="99"/>
+      <c r="Z4" s="99"/>
+      <c r="AA4" s="99"/>
+      <c r="AB4" s="99"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>46076</v>
       </c>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
-      <c r="AH4" s="100"/>
-      <c r="AI4" s="100"/>
-      <c r="AJ4" s="100"/>
-      <c r="AK4" s="100">
+      <c r="AE4" s="99"/>
+      <c r="AF4" s="99"/>
+      <c r="AG4" s="99"/>
+      <c r="AH4" s="99"/>
+      <c r="AI4" s="99"/>
+      <c r="AJ4" s="99"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>46083</v>
       </c>
-      <c r="AL4" s="100"/>
-      <c r="AM4" s="100"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="100"/>
-      <c r="AP4" s="100"/>
-      <c r="AQ4" s="100"/>
-      <c r="AR4" s="100">
+      <c r="AL4" s="99"/>
+      <c r="AM4" s="99"/>
+      <c r="AN4" s="99"/>
+      <c r="AO4" s="99"/>
+      <c r="AP4" s="99"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>46090</v>
       </c>
-      <c r="AS4" s="100"/>
-      <c r="AT4" s="100"/>
-      <c r="AU4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="100"/>
-      <c r="AX4" s="100"/>
-      <c r="AY4" s="100">
+      <c r="AS4" s="99"/>
+      <c r="AT4" s="99"/>
+      <c r="AU4" s="99"/>
+      <c r="AV4" s="99"/>
+      <c r="AW4" s="99"/>
+      <c r="AX4" s="99"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>46097</v>
       </c>
-      <c r="AZ4" s="100"/>
-      <c r="BA4" s="100"/>
-      <c r="BB4" s="100"/>
-      <c r="BC4" s="100"/>
-      <c r="BD4" s="100"/>
-      <c r="BE4" s="100"/>
-      <c r="BF4" s="100">
+      <c r="AZ4" s="99"/>
+      <c r="BA4" s="99"/>
+      <c r="BB4" s="99"/>
+      <c r="BC4" s="99"/>
+      <c r="BD4" s="99"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>46104</v>
       </c>
-      <c r="BG4" s="100"/>
-      <c r="BH4" s="100"/>
-      <c r="BI4" s="100"/>
-      <c r="BJ4" s="100"/>
-      <c r="BK4" s="100"/>
-      <c r="BL4" s="101"/>
-    </row>
-    <row r="5" spans="1:64" s="21" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="107"/>
-      <c r="B5" s="108" t="s">
+      <c r="BG4" s="99"/>
+      <c r="BH4" s="99"/>
+      <c r="BI4" s="99"/>
+      <c r="BJ4" s="99"/>
+      <c r="BK4" s="99"/>
+      <c r="BL4" s="100"/>
+    </row>
+    <row r="5" spans="1:64" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="109"/>
+      <c r="B5" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="110" t="s">
+      <c r="C5" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="103" t="s">
+      <c r="E5" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="103" t="s">
+      <c r="F5" s="102" t="s">
         <v>10</v>
       </c>
       <c r="I5" s="26">
@@ -2115,13 +2112,13 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="6" spans="1:64" s="21" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="107"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
+    <row r="6" spans="1:64" s="21" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="109"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
       <c r="I6" s="29" t="str">
         <f t="shared" ref="I6:AN6" si="3">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -2347,7 +2344,7 @@
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:64" s="21" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1">
+    <row r="7" spans="1:64" s="21" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
@@ -2357,7 +2354,7 @@
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
       <c r="H7" s="21" t="str">
-        <f ca="1">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I7" s="34"/>
@@ -2417,7 +2414,7 @@
       <c r="BK7" s="34"/>
       <c r="BL7" s="34"/>
     </row>
-    <row r="8" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="8" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="35" t="s">
         <v>12</v>
@@ -2428,7 +2425,7 @@
       <c r="F8" s="39"/>
       <c r="G8" s="17"/>
       <c r="H8" s="5" t="str">
-        <f t="shared" ref="H8:H31" ca="1" si="5">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H8:H31" si="5">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I8" s="40"/>
@@ -2488,7 +2485,7 @@
       <c r="BK8" s="40"/>
       <c r="BL8" s="40"/>
     </row>
-    <row r="9" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="9" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="42" t="s">
         <v>13</v>
@@ -2497,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="45">
         <f>Project_Start+14</f>
@@ -2509,7 +2506,7 @@
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I9" s="46"/>
@@ -2569,7 +2566,7 @@
       <c r="BK9" s="46"/>
       <c r="BL9" s="46"/>
     </row>
-    <row r="10" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="10" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="47" t="s">
         <v>15</v>
@@ -2577,10 +2574,10 @@
       <c r="C10" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="49">
-        <v>0</v>
-      </c>
-      <c r="E10" s="50">
+      <c r="D10" s="44">
+        <v>1</v>
+      </c>
+      <c r="E10" s="49">
         <f>E9</f>
         <v>46073</v>
       </c>
@@ -2590,7 +2587,7 @@
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I10" s="46"/>
@@ -2605,8 +2602,8 @@
       <c r="R10" s="46"/>
       <c r="S10" s="46"/>
       <c r="T10" s="46"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="51"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="50"/>
       <c r="W10" s="46"/>
       <c r="X10" s="46"/>
       <c r="Y10" s="46"/>
@@ -2650,7 +2647,7 @@
       <c r="BK10" s="46"/>
       <c r="BL10" s="46"/>
     </row>
-    <row r="11" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="11" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="47" t="s">
         <v>16</v>
@@ -2658,10 +2655,10 @@
       <c r="C11" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="44">
         <v>1</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="49">
         <f>E10-2</f>
         <v>46071</v>
       </c>
@@ -2671,7 +2668,7 @@
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I11" s="46"/>
@@ -2731,7 +2728,7 @@
       <c r="BK11" s="46"/>
       <c r="BL11" s="46"/>
     </row>
-    <row r="12" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="12" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="47" t="s">
         <v>18</v>
@@ -2739,10 +2736,10 @@
       <c r="C12" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="49">
-        <v>0</v>
-      </c>
-      <c r="E12" s="50">
+      <c r="D12" s="44">
+        <v>1</v>
+      </c>
+      <c r="E12" s="49">
         <f>E11+2</f>
         <v>46073</v>
       </c>
@@ -2752,7 +2749,7 @@
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I12" s="46"/>
@@ -2771,7 +2768,7 @@
       <c r="V12" s="46"/>
       <c r="W12" s="46"/>
       <c r="X12" s="46"/>
-      <c r="Y12" s="51"/>
+      <c r="Y12" s="50"/>
       <c r="Z12" s="46"/>
       <c r="AA12" s="46"/>
       <c r="AB12" s="46"/>
@@ -2812,43 +2809,43 @@
       <c r="BK12" s="46"/>
       <c r="BL12" s="46"/>
     </row>
-    <row r="13" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="13" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="53"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="56"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
       <c r="G13" s="17"/>
       <c r="H13" s="5" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="14" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="59">
+      <c r="D14" s="58">
         <v>1</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="59">
         <f>Project_Start</f>
         <v>46059</v>
       </c>
-      <c r="F14" s="60">
+      <c r="F14" s="59">
         <f>E14+7</f>
         <v>46066</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="I14" s="46"/>
@@ -2908,28 +2905,28 @@
       <c r="BK14" s="46"/>
       <c r="BL14" s="46"/>
     </row>
-    <row r="15" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="15" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="58">
         <v>1</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="59">
         <f>Project_Start+7</f>
         <v>46066</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="59">
         <f>E15+4</f>
         <v>46070</v>
       </c>
       <c r="G15" s="17"/>
       <c r="H15" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I15" s="46"/>
@@ -2944,8 +2941,8 @@
       <c r="R15" s="46"/>
       <c r="S15" s="46"/>
       <c r="T15" s="46"/>
-      <c r="U15" s="51"/>
-      <c r="V15" s="51"/>
+      <c r="U15" s="50"/>
+      <c r="V15" s="50"/>
       <c r="W15" s="46"/>
       <c r="X15" s="46"/>
       <c r="Y15" s="46"/>
@@ -2989,22 +2986,22 @@
       <c r="BK15" s="46"/>
       <c r="BL15" s="46"/>
     </row>
-    <row r="16" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="16" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="60">
+      <c r="B16" s="56"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="59">
         <f>F15</f>
         <v>46070</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="59">
         <f>E16+3</f>
         <v>46073</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I16" s="46"/>
@@ -3064,99 +3061,99 @@
       <c r="BK16" s="46"/>
       <c r="BL16" s="46"/>
     </row>
-    <row r="17" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="17" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="65"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="64"/>
       <c r="G17" s="17"/>
       <c r="H17" s="5" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="66"/>
-      <c r="M17" s="66"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-      <c r="U17" s="66"/>
-      <c r="V17" s="66"/>
-      <c r="W17" s="66"/>
-      <c r="X17" s="66"/>
-      <c r="Y17" s="66"/>
-      <c r="Z17" s="66"/>
-      <c r="AA17" s="66"/>
-      <c r="AB17" s="66"/>
-      <c r="AC17" s="66"/>
-      <c r="AD17" s="66"/>
-      <c r="AE17" s="66"/>
-      <c r="AF17" s="66"/>
-      <c r="AG17" s="66"/>
-      <c r="AH17" s="66"/>
-      <c r="AI17" s="66"/>
-      <c r="AJ17" s="66"/>
-      <c r="AK17" s="66"/>
-      <c r="AL17" s="66"/>
-      <c r="AM17" s="66"/>
-      <c r="AN17" s="66"/>
-      <c r="AO17" s="66"/>
-      <c r="AP17" s="66"/>
-      <c r="AQ17" s="66"/>
-      <c r="AR17" s="66"/>
-      <c r="AS17" s="66"/>
-      <c r="AT17" s="66"/>
-      <c r="AU17" s="66"/>
-      <c r="AV17" s="66"/>
-      <c r="AW17" s="66"/>
-      <c r="AX17" s="66"/>
-      <c r="AY17" s="66"/>
-      <c r="AZ17" s="66"/>
-      <c r="BA17" s="66"/>
-      <c r="BB17" s="66"/>
-      <c r="BC17" s="66"/>
-      <c r="BD17" s="66"/>
-      <c r="BE17" s="66"/>
-      <c r="BF17" s="66"/>
-      <c r="BG17" s="66"/>
-      <c r="BH17" s="66"/>
-      <c r="BI17" s="66"/>
-      <c r="BJ17" s="66"/>
-      <c r="BK17" s="66"/>
-      <c r="BL17" s="66"/>
-    </row>
-    <row r="18" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="65"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="65"/>
+      <c r="X17" s="65"/>
+      <c r="Y17" s="65"/>
+      <c r="Z17" s="65"/>
+      <c r="AA17" s="65"/>
+      <c r="AB17" s="65"/>
+      <c r="AC17" s="65"/>
+      <c r="AD17" s="65"/>
+      <c r="AE17" s="65"/>
+      <c r="AF17" s="65"/>
+      <c r="AG17" s="65"/>
+      <c r="AH17" s="65"/>
+      <c r="AI17" s="65"/>
+      <c r="AJ17" s="65"/>
+      <c r="AK17" s="65"/>
+      <c r="AL17" s="65"/>
+      <c r="AM17" s="65"/>
+      <c r="AN17" s="65"/>
+      <c r="AO17" s="65"/>
+      <c r="AP17" s="65"/>
+      <c r="AQ17" s="65"/>
+      <c r="AR17" s="65"/>
+      <c r="AS17" s="65"/>
+      <c r="AT17" s="65"/>
+      <c r="AU17" s="65"/>
+      <c r="AV17" s="65"/>
+      <c r="AW17" s="65"/>
+      <c r="AX17" s="65"/>
+      <c r="AY17" s="65"/>
+      <c r="AZ17" s="65"/>
+      <c r="BA17" s="65"/>
+      <c r="BB17" s="65"/>
+      <c r="BC17" s="65"/>
+      <c r="BD17" s="65"/>
+      <c r="BE17" s="65"/>
+      <c r="BF17" s="65"/>
+      <c r="BG17" s="65"/>
+      <c r="BH17" s="65"/>
+      <c r="BI17" s="65"/>
+      <c r="BJ17" s="65"/>
+      <c r="BK17" s="65"/>
+      <c r="BL17" s="65"/>
+    </row>
+    <row r="18" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="69">
+      <c r="D18" s="68">
         <v>1</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="69">
         <f>Project_Start+7</f>
         <v>46066</v>
       </c>
-      <c r="F18" s="70">
+      <c r="F18" s="69">
         <f>E18+11</f>
         <v>46077</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I18" s="46"/>
@@ -3216,28 +3213,28 @@
       <c r="BK18" s="46"/>
       <c r="BL18" s="46"/>
     </row>
-    <row r="19" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="19" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="69">
+      <c r="D19" s="68">
         <v>1</v>
       </c>
-      <c r="E19" s="70">
+      <c r="E19" s="69">
         <f>Project_Start+8</f>
         <v>46067</v>
       </c>
-      <c r="F19" s="70">
+      <c r="F19" s="69">
         <f>E19+1</f>
         <v>46068</v>
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I19" s="46"/>
@@ -3297,28 +3294,28 @@
       <c r="BK19" s="46"/>
       <c r="BL19" s="46"/>
     </row>
-    <row r="20" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="20" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="68">
         <v>1</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="69">
         <f>E19</f>
         <v>46067</v>
       </c>
-      <c r="F20" s="70">
+      <c r="F20" s="69">
         <f>E20+2</f>
         <v>46069</v>
       </c>
       <c r="G20" s="17"/>
       <c r="H20" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I20" s="46"/>
@@ -3378,22 +3375,22 @@
       <c r="BK20" s="46"/>
       <c r="BL20" s="46"/>
     </row>
-    <row r="21" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="21" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="69">
+      <c r="D21" s="68">
         <v>1</v>
       </c>
-      <c r="E21" s="70">
+      <c r="E21" s="69">
         <f>E20+2</f>
         <v>46069</v>
       </c>
-      <c r="F21" s="70">
+      <c r="F21" s="69">
         <f>E21+1</f>
         <v>46070</v>
       </c>
@@ -3456,28 +3453,28 @@
       <c r="BK21" s="46"/>
       <c r="BL21" s="46"/>
     </row>
-    <row r="22" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="22" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="69">
+      <c r="D22" s="68">
         <v>1</v>
       </c>
-      <c r="E22" s="70">
+      <c r="E22" s="69">
         <f>F20</f>
         <v>46069</v>
       </c>
-      <c r="F22" s="70">
+      <c r="F22" s="69">
         <f>E22+2</f>
         <v>46071</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I22" s="46"/>
@@ -3537,28 +3534,28 @@
       <c r="BK22" s="46"/>
       <c r="BL22" s="46"/>
     </row>
-    <row r="23" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="23" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="69">
+      <c r="D23" s="68">
         <v>1</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E23" s="69">
         <f>F22</f>
         <v>46071</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F23" s="69">
         <f>E23</f>
         <v>46071</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I23" s="46"/>
@@ -3618,99 +3615,99 @@
       <c r="BK23" s="46"/>
       <c r="BL23" s="46"/>
     </row>
-    <row r="24" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="24" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
-      <c r="B24" s="71" t="s">
+      <c r="B24" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="75"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="74"/>
       <c r="G24" s="17"/>
       <c r="H24" s="5" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="76"/>
-      <c r="Q24" s="76"/>
-      <c r="R24" s="76"/>
-      <c r="S24" s="76"/>
-      <c r="T24" s="76"/>
-      <c r="U24" s="76"/>
-      <c r="V24" s="76"/>
-      <c r="W24" s="76"/>
-      <c r="X24" s="76"/>
-      <c r="Y24" s="76"/>
-      <c r="Z24" s="76"/>
-      <c r="AA24" s="76"/>
-      <c r="AB24" s="76"/>
-      <c r="AC24" s="76"/>
-      <c r="AD24" s="76"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="76"/>
-      <c r="AG24" s="76"/>
-      <c r="AH24" s="76"/>
-      <c r="AI24" s="76"/>
-      <c r="AJ24" s="76"/>
-      <c r="AK24" s="76"/>
-      <c r="AL24" s="76"/>
-      <c r="AM24" s="76"/>
-      <c r="AN24" s="76"/>
-      <c r="AO24" s="76"/>
-      <c r="AP24" s="76"/>
-      <c r="AQ24" s="76"/>
-      <c r="AR24" s="76"/>
-      <c r="AS24" s="76"/>
-      <c r="AT24" s="76"/>
-      <c r="AU24" s="76"/>
-      <c r="AV24" s="76"/>
-      <c r="AW24" s="76"/>
-      <c r="AX24" s="76"/>
-      <c r="AY24" s="76"/>
-      <c r="AZ24" s="76"/>
-      <c r="BA24" s="76"/>
-      <c r="BB24" s="76"/>
-      <c r="BC24" s="76"/>
-      <c r="BD24" s="76"/>
-      <c r="BE24" s="76"/>
-      <c r="BF24" s="76"/>
-      <c r="BG24" s="76"/>
-      <c r="BH24" s="76"/>
-      <c r="BI24" s="76"/>
-      <c r="BJ24" s="76"/>
-      <c r="BK24" s="76"/>
-      <c r="BL24" s="76"/>
-    </row>
-    <row r="25" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="75"/>
+      <c r="T24" s="75"/>
+      <c r="U24" s="75"/>
+      <c r="V24" s="75"/>
+      <c r="W24" s="75"/>
+      <c r="X24" s="75"/>
+      <c r="Y24" s="75"/>
+      <c r="Z24" s="75"/>
+      <c r="AA24" s="75"/>
+      <c r="AB24" s="75"/>
+      <c r="AC24" s="75"/>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="75"/>
+      <c r="AF24" s="75"/>
+      <c r="AG24" s="75"/>
+      <c r="AH24" s="75"/>
+      <c r="AI24" s="75"/>
+      <c r="AJ24" s="75"/>
+      <c r="AK24" s="75"/>
+      <c r="AL24" s="75"/>
+      <c r="AM24" s="75"/>
+      <c r="AN24" s="75"/>
+      <c r="AO24" s="75"/>
+      <c r="AP24" s="75"/>
+      <c r="AQ24" s="75"/>
+      <c r="AR24" s="75"/>
+      <c r="AS24" s="75"/>
+      <c r="AT24" s="75"/>
+      <c r="AU24" s="75"/>
+      <c r="AV24" s="75"/>
+      <c r="AW24" s="75"/>
+      <c r="AX24" s="75"/>
+      <c r="AY24" s="75"/>
+      <c r="AZ24" s="75"/>
+      <c r="BA24" s="75"/>
+      <c r="BB24" s="75"/>
+      <c r="BC24" s="75"/>
+      <c r="BD24" s="75"/>
+      <c r="BE24" s="75"/>
+      <c r="BF24" s="75"/>
+      <c r="BG24" s="75"/>
+      <c r="BH24" s="75"/>
+      <c r="BI24" s="75"/>
+      <c r="BJ24" s="75"/>
+      <c r="BK24" s="75"/>
+      <c r="BL24" s="75"/>
+    </row>
+    <row r="25" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
-      <c r="B25" s="77" t="s">
+      <c r="B25" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="78" t="s">
+      <c r="C25" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="79">
+      <c r="D25" s="78">
         <v>1</v>
       </c>
-      <c r="E25" s="80">
+      <c r="E25" s="79">
         <f>Project_Start+12</f>
         <v>46071</v>
       </c>
-      <c r="F25" s="80">
+      <c r="F25" s="79">
         <f>E25+6</f>
         <v>46077</v>
       </c>
       <c r="G25" s="17"/>
       <c r="H25" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="I25" s="46"/>
@@ -3770,28 +3767,28 @@
       <c r="BK25" s="46"/>
       <c r="BL25" s="46"/>
     </row>
-    <row r="26" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="26" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="78" t="s">
+      <c r="C26" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="79">
+      <c r="D26" s="78">
         <v>1</v>
       </c>
-      <c r="E26" s="80">
+      <c r="E26" s="79">
         <f>Project_Start+12</f>
         <v>46071</v>
       </c>
-      <c r="F26" s="80">
+      <c r="F26" s="79">
         <f>E26+2</f>
         <v>46073</v>
       </c>
       <c r="G26" s="17"/>
       <c r="H26" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I26" s="46"/>
@@ -3851,28 +3848,28 @@
       <c r="BK26" s="46"/>
       <c r="BL26" s="46"/>
     </row>
-    <row r="27" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="27" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="78" t="s">
+      <c r="C27" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="79">
+      <c r="D27" s="78">
         <v>1</v>
       </c>
-      <c r="E27" s="80">
+      <c r="E27" s="79">
         <f>Project_Start+13</f>
         <v>46072</v>
       </c>
-      <c r="F27" s="80">
+      <c r="F27" s="79">
         <f>E27+2</f>
         <v>46074</v>
       </c>
       <c r="G27" s="17"/>
       <c r="H27" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I27" s="46"/>
@@ -3932,28 +3929,28 @@
       <c r="BK27" s="46"/>
       <c r="BL27" s="46"/>
     </row>
-    <row r="28" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="28" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
-      <c r="B28" s="77" t="s">
+      <c r="B28" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="78" t="s">
+      <c r="C28" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="79">
+      <c r="D28" s="78">
         <v>1</v>
       </c>
-      <c r="E28" s="80">
+      <c r="E28" s="79">
         <f>Project_Start+13</f>
         <v>46072</v>
       </c>
-      <c r="F28" s="80">
+      <c r="F28" s="79">
         <f>E28+3</f>
         <v>46075</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I28" s="46"/>
@@ -4013,28 +4010,28 @@
       <c r="BK28" s="46"/>
       <c r="BL28" s="46"/>
     </row>
-    <row r="29" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="29" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
-      <c r="B29" s="77" t="s">
+      <c r="B29" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="78" t="s">
+      <c r="C29" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="79">
+      <c r="D29" s="78">
         <v>1</v>
       </c>
-      <c r="E29" s="80">
+      <c r="E29" s="79">
         <f>Project_Start+16</f>
         <v>46075</v>
       </c>
-      <c r="F29" s="80">
+      <c r="F29" s="79">
         <f>E29+1</f>
         <v>46076</v>
       </c>
       <c r="G29" s="17"/>
       <c r="H29" s="5">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I29" s="46"/>
@@ -4094,16 +4091,16 @@
       <c r="BK29" s="46"/>
       <c r="BL29" s="46"/>
     </row>
-    <row r="30" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="30" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
       <c r="G30" s="17"/>
       <c r="H30" s="5" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="I30" s="40"/>
@@ -4163,85 +4160,85 @@
       <c r="BK30" s="40"/>
       <c r="BL30" s="40"/>
     </row>
-    <row r="31" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="31" spans="1:64" s="41" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
-      <c r="B31" s="85" t="s">
+      <c r="B31" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="86"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="89"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="88"/>
       <c r="G31" s="17"/>
       <c r="H31" s="6" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="I31" s="90"/>
-      <c r="J31" s="90"/>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90"/>
-      <c r="M31" s="90"/>
-      <c r="N31" s="90"/>
-      <c r="O31" s="90"/>
-      <c r="P31" s="90"/>
-      <c r="Q31" s="90"/>
-      <c r="R31" s="90"/>
-      <c r="S31" s="90"/>
-      <c r="T31" s="90"/>
-      <c r="U31" s="90"/>
-      <c r="V31" s="90"/>
-      <c r="W31" s="90"/>
-      <c r="X31" s="90"/>
-      <c r="Y31" s="90"/>
-      <c r="Z31" s="90"/>
-      <c r="AA31" s="90"/>
-      <c r="AB31" s="90"/>
-      <c r="AC31" s="90"/>
-      <c r="AD31" s="90"/>
-      <c r="AE31" s="90"/>
-      <c r="AF31" s="90"/>
-      <c r="AG31" s="90"/>
-      <c r="AH31" s="90"/>
-      <c r="AI31" s="90"/>
-      <c r="AJ31" s="90"/>
-      <c r="AK31" s="90"/>
-      <c r="AL31" s="90"/>
-      <c r="AM31" s="90"/>
-      <c r="AN31" s="90"/>
-      <c r="AO31" s="90"/>
-      <c r="AP31" s="90"/>
-      <c r="AQ31" s="90"/>
-      <c r="AR31" s="90"/>
-      <c r="AS31" s="90"/>
-      <c r="AT31" s="90"/>
-      <c r="AU31" s="90"/>
-      <c r="AV31" s="90"/>
-      <c r="AW31" s="90"/>
-      <c r="AX31" s="90"/>
-      <c r="AY31" s="90"/>
-      <c r="AZ31" s="90"/>
-      <c r="BA31" s="90"/>
-      <c r="BB31" s="90"/>
-      <c r="BC31" s="90"/>
-      <c r="BD31" s="90"/>
-      <c r="BE31" s="90"/>
-      <c r="BF31" s="90"/>
-      <c r="BG31" s="90"/>
-      <c r="BH31" s="90"/>
-      <c r="BI31" s="90"/>
-      <c r="BJ31" s="90"/>
-      <c r="BK31" s="90"/>
-      <c r="BL31" s="90"/>
-    </row>
-    <row r="32" spans="1:64" ht="30" customHeight="1">
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
+      <c r="M31" s="89"/>
+      <c r="N31" s="89"/>
+      <c r="O31" s="89"/>
+      <c r="P31" s="89"/>
+      <c r="Q31" s="89"/>
+      <c r="R31" s="89"/>
+      <c r="S31" s="89"/>
+      <c r="T31" s="89"/>
+      <c r="U31" s="89"/>
+      <c r="V31" s="89"/>
+      <c r="W31" s="89"/>
+      <c r="X31" s="89"/>
+      <c r="Y31" s="89"/>
+      <c r="Z31" s="89"/>
+      <c r="AA31" s="89"/>
+      <c r="AB31" s="89"/>
+      <c r="AC31" s="89"/>
+      <c r="AD31" s="89"/>
+      <c r="AE31" s="89"/>
+      <c r="AF31" s="89"/>
+      <c r="AG31" s="89"/>
+      <c r="AH31" s="89"/>
+      <c r="AI31" s="89"/>
+      <c r="AJ31" s="89"/>
+      <c r="AK31" s="89"/>
+      <c r="AL31" s="89"/>
+      <c r="AM31" s="89"/>
+      <c r="AN31" s="89"/>
+      <c r="AO31" s="89"/>
+      <c r="AP31" s="89"/>
+      <c r="AQ31" s="89"/>
+      <c r="AR31" s="89"/>
+      <c r="AS31" s="89"/>
+      <c r="AT31" s="89"/>
+      <c r="AU31" s="89"/>
+      <c r="AV31" s="89"/>
+      <c r="AW31" s="89"/>
+      <c r="AX31" s="89"/>
+      <c r="AY31" s="89"/>
+      <c r="AZ31" s="89"/>
+      <c r="BA31" s="89"/>
+      <c r="BB31" s="89"/>
+      <c r="BC31" s="89"/>
+      <c r="BD31" s="89"/>
+      <c r="BE31" s="89"/>
+      <c r="BF31" s="89"/>
+      <c r="BG31" s="89"/>
+      <c r="BH31" s="89"/>
+      <c r="BI31" s="89"/>
+      <c r="BJ31" s="89"/>
+      <c r="BK31" s="89"/>
+      <c r="BL31" s="89"/>
+    </row>
+    <row r="32" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="3:6" ht="30" customHeight="1">
+    <row r="33" spans="3:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="16"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="30" customHeight="1">
+    <row r="34" spans="3:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="4"/>
     </row>
   </sheetData>
@@ -4372,111 +4369,111 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="87" style="7" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1"/>
-    <row r="2" spans="1:2" s="9" customFormat="1" ht="15.6">
-      <c r="A2" s="91" t="s">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:2" s="9" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="90" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:2" s="11" customFormat="1" ht="27" customHeight="1">
-      <c r="A3" s="92"/>
+    <row r="3" spans="1:2" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="91"/>
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:2" s="10" customFormat="1" ht="30">
-      <c r="A4" s="93" t="s">
+    <row r="4" spans="1:2" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.6">
+      <c r="A4" s="92" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74.25" customHeight="1">
-      <c r="A5" s="94" t="s">
+    <row r="5" spans="1:2" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="93" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1">
-      <c r="A6" s="93" t="s">
+    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="92" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="7" customFormat="1" ht="205.15" customHeight="1">
-      <c r="A7" s="95" t="s">
+    <row r="7" spans="1:2" s="7" customFormat="1" ht="205.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="94" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="10" customFormat="1" ht="30">
-      <c r="A8" s="93" t="s">
+    <row r="8" spans="1:2" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.6">
+      <c r="A8" s="92" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="41.45">
-      <c r="A9" s="94" t="s">
+    <row r="9" spans="1:2" ht="57" x14ac:dyDescent="0.2">
+      <c r="A9" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="7" customFormat="1" ht="28.15" customHeight="1">
-      <c r="A10" s="96" t="s">
+    <row r="10" spans="1:2" s="7" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="95" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="10" customFormat="1" ht="30">
-      <c r="A11" s="93" t="s">
+    <row r="11" spans="1:2" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.6">
+      <c r="A11" s="92" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="27.6">
-      <c r="A12" s="94" t="s">
+    <row r="12" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="93" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="7" customFormat="1" ht="28.15" customHeight="1">
-      <c r="A13" s="96" t="s">
+    <row r="13" spans="1:2" s="7" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="95" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="10" customFormat="1" ht="30">
-      <c r="A14" s="93" t="s">
+    <row r="14" spans="1:2" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.6">
+      <c r="A14" s="92" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="75" customHeight="1">
-      <c r="A15" s="94" t="s">
+    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="93" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="69">
-      <c r="A16" s="94" t="s">
+    <row r="16" spans="1:2" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="93" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="97"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="97"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="97"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="97"/>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="97"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="97"/>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="97"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="97"/>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="96"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="96"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="96"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="96"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="96"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="96"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="96"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="96"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4684,15 +4681,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CBD4C02-554B-4D0B-B979-B19373D764DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CBD4C02-554B-4D0B-B979-B19373D764DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d94ee4e4-02cb-4da0-9dbe-ce518434d583"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d94ee4e4-02cb-4da0-9dbe-ce518434d583"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
